--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122286914</v>
+        <v>122286962</v>
       </c>
       <c r="B2" t="n">
-        <v>57214</v>
+        <v>57708</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100096</v>
+        <v>103008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338023</v>
+        <v>338073</v>
       </c>
       <c r="R2" t="n">
-        <v>6489720</v>
+        <v>6489723</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286962</v>
+        <v>122286914</v>
       </c>
       <c r="B3" t="n">
-        <v>57706</v>
+        <v>57216</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,20 +812,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>100096</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,21 +838,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338073</v>
+        <v>338023</v>
       </c>
       <c r="R3" t="n">
-        <v>6489723</v>
+        <v>6489720</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +889,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122286957</v>
+        <v>122286958</v>
       </c>
       <c r="B4" t="n">
-        <v>57467</v>
+        <v>57779</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102626</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,11 +963,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>obs i häcktid, lämplig biotop</t>
@@ -979,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337947</v>
+        <v>337979</v>
       </c>
       <c r="R4" t="n">
-        <v>6489822</v>
+        <v>6489830</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1060,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122286958</v>
+        <v>122286957</v>
       </c>
       <c r="B5" t="n">
-        <v>57777</v>
+        <v>57469</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,20 +1067,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103037</v>
+        <v>102626</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1098,6 +1093,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>obs i häcktid, lämplig biotop</t>
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337979</v>
+        <v>337947</v>
       </c>
       <c r="R5" t="n">
-        <v>6489830</v>
+        <v>6489822</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1193,7 +1193,7 @@
         <v>122286959</v>
       </c>
       <c r="B6" t="n">
-        <v>57875</v>
+        <v>57877</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286914</v>
+        <v>122286957</v>
       </c>
       <c r="B3" t="n">
-        <v>57216</v>
+        <v>57469</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100096</v>
+        <v>102626</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,16 +838,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338023</v>
+        <v>337947</v>
       </c>
       <c r="R3" t="n">
-        <v>6489720</v>
+        <v>6489822</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -925,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122286958</v>
+        <v>122286914</v>
       </c>
       <c r="B4" t="n">
-        <v>57779</v>
+        <v>57216</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>100096</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,21 +973,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337979</v>
+        <v>338023</v>
       </c>
       <c r="R4" t="n">
-        <v>6489830</v>
+        <v>6489720</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1055,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122286957</v>
+        <v>122286958</v>
       </c>
       <c r="B5" t="n">
-        <v>57469</v>
+        <v>57779</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,20 +1072,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102626</v>
+        <v>103037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1093,11 +1098,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>obs i häcktid, lämplig biotop</t>
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337947</v>
+        <v>337979</v>
       </c>
       <c r="R5" t="n">
-        <v>6489822</v>
+        <v>6489830</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -1060,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122286959</v>
+        <v>122286958</v>
       </c>
       <c r="B5" t="n">
-        <v>57877</v>
+        <v>57779</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,40 +1072,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102995</v>
+        <v>103037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1114,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337961</v>
+        <v>337979</v>
       </c>
       <c r="R5" t="n">
-        <v>6489866</v>
+        <v>6489830</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1149,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,7 +1154,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122286958</v>
+        <v>122286959</v>
       </c>
       <c r="B6" t="n">
-        <v>57779</v>
+        <v>57877</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1202,35 +1202,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103037</v>
+        <v>102995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1239,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337979</v>
+        <v>337961</v>
       </c>
       <c r="R6" t="n">
-        <v>6489830</v>
+        <v>6489866</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1274,7 +1279,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,12 +1289,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:39</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122286914</v>
+        <v>122286958</v>
       </c>
       <c r="B2" t="n">
-        <v>57216</v>
+        <v>57779</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100096</v>
+        <v>103037</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338023</v>
+        <v>337979</v>
       </c>
       <c r="R2" t="n">
-        <v>6489720</v>
+        <v>6489830</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286962</v>
+        <v>122286959</v>
       </c>
       <c r="B3" t="n">
-        <v>57708</v>
+        <v>57877</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,16 +821,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>102995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,7 +840,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -849,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338073</v>
+        <v>337961</v>
       </c>
       <c r="R3" t="n">
-        <v>6489723</v>
+        <v>6489866</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122286957</v>
+        <v>122286914</v>
       </c>
       <c r="B4" t="n">
-        <v>57469</v>
+        <v>57216</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102626</v>
+        <v>100096</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,26 +973,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337947</v>
+        <v>338023</v>
       </c>
       <c r="R4" t="n">
-        <v>6489822</v>
+        <v>6489720</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1060,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122286958</v>
+        <v>122286962</v>
       </c>
       <c r="B5" t="n">
-        <v>57779</v>
+        <v>57708</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,25 +1072,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103037</v>
+        <v>103008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337979</v>
+        <v>338073</v>
       </c>
       <c r="R5" t="n">
-        <v>6489830</v>
+        <v>6489723</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,12 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:39</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,10 +1185,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122286959</v>
+        <v>122286957</v>
       </c>
       <c r="B6" t="n">
-        <v>57877</v>
+        <v>57469</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1202,40 +1197,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102995</v>
+        <v>102626</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337961</v>
+        <v>337947</v>
       </c>
       <c r="R6" t="n">
-        <v>6489866</v>
+        <v>6489822</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1279,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1289,7 +1284,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122286958</v>
+        <v>122286914</v>
       </c>
       <c r="B2" t="n">
-        <v>57779</v>
+        <v>57216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103037</v>
+        <v>100096</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337979</v>
+        <v>338023</v>
       </c>
       <c r="R2" t="n">
-        <v>6489830</v>
+        <v>6489720</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286959</v>
+        <v>122286957</v>
       </c>
       <c r="B3" t="n">
-        <v>57877</v>
+        <v>57469</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,40 +812,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102995</v>
+        <v>102626</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337961</v>
+        <v>337947</v>
       </c>
       <c r="R3" t="n">
-        <v>6489866</v>
+        <v>6489822</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +899,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122286914</v>
+        <v>122286958</v>
       </c>
       <c r="B4" t="n">
-        <v>57216</v>
+        <v>57779</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100096</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,16 +973,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338023</v>
+        <v>337979</v>
       </c>
       <c r="R4" t="n">
-        <v>6489720</v>
+        <v>6489830</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1014,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1060,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122286962</v>
+        <v>122286959</v>
       </c>
       <c r="B5" t="n">
-        <v>57708</v>
+        <v>57877</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,16 +1081,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103008</v>
+        <v>102995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1095,7 +1100,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1109,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338073</v>
+        <v>337961</v>
       </c>
       <c r="R5" t="n">
-        <v>6489723</v>
+        <v>6489866</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1144,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122286957</v>
+        <v>122286962</v>
       </c>
       <c r="B6" t="n">
-        <v>57469</v>
+        <v>57708</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,25 +1207,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102626</v>
+        <v>103008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1223,14 +1233,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1239,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337947</v>
+        <v>338073</v>
       </c>
       <c r="R6" t="n">
-        <v>6489822</v>
+        <v>6489723</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1274,7 +1279,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,12 +1289,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:39</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122286914</v>
+        <v>122286957</v>
       </c>
       <c r="B2" t="n">
-        <v>57216</v>
+        <v>57474</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100096</v>
+        <v>102626</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338023</v>
+        <v>337947</v>
       </c>
       <c r="R2" t="n">
-        <v>6489720</v>
+        <v>6489822</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286957</v>
+        <v>122286962</v>
       </c>
       <c r="B3" t="n">
-        <v>57469</v>
+        <v>57713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102626</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,14 +848,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337947</v>
+        <v>338073</v>
       </c>
       <c r="R3" t="n">
-        <v>6489822</v>
+        <v>6489723</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,12 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,7 +938,7 @@
         <v>122286958</v>
       </c>
       <c r="B4" t="n">
-        <v>57779</v>
+        <v>57784</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>122286959</v>
       </c>
       <c r="B5" t="n">
-        <v>57877</v>
+        <v>57882</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122286962</v>
+        <v>122286914</v>
       </c>
       <c r="B6" t="n">
-        <v>57708</v>
+        <v>57221</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,20 +1207,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103008</v>
+        <v>100096</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1233,21 +1233,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338073</v>
+        <v>338023</v>
       </c>
       <c r="R6" t="n">
-        <v>6489723</v>
+        <v>6489720</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1279,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1289,7 +1284,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122286957</v>
+        <v>122286959</v>
       </c>
       <c r="B2" t="n">
-        <v>57474</v>
+        <v>57882</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102626</v>
+        <v>102995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337947</v>
+        <v>337961</v>
       </c>
       <c r="R2" t="n">
-        <v>6489822</v>
+        <v>6489866</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:39</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286962</v>
+        <v>122286914</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>57221</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,20 +817,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>100096</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -848,21 +843,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338073</v>
+        <v>338023</v>
       </c>
       <c r="R3" t="n">
-        <v>6489723</v>
+        <v>6489720</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +894,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1065,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122286959</v>
+        <v>122286957</v>
       </c>
       <c r="B5" t="n">
-        <v>57882</v>
+        <v>57474</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,40 +1072,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102995</v>
+        <v>102626</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1119,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337961</v>
+        <v>337947</v>
       </c>
       <c r="R5" t="n">
-        <v>6489866</v>
+        <v>6489822</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1154,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1159,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122286914</v>
+        <v>122286962</v>
       </c>
       <c r="B6" t="n">
-        <v>57221</v>
+        <v>57713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,20 +1207,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100096</v>
+        <v>103008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1233,16 +1233,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338023</v>
+        <v>338073</v>
       </c>
       <c r="R6" t="n">
-        <v>6489720</v>
+        <v>6489723</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1274,7 +1279,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,12 +1289,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122286959</v>
+        <v>122286914</v>
       </c>
       <c r="B2" t="n">
-        <v>57882</v>
+        <v>57221</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102995</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Buskskvätta</t>
-        </is>
+        <v>100096</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,17 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337961</v>
+        <v>338023</v>
       </c>
       <c r="R2" t="n">
-        <v>6489866</v>
+        <v>6489720</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +759,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286914</v>
+        <v>122286959</v>
       </c>
       <c r="B3" t="n">
-        <v>57221</v>
+        <v>57882</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,20 +807,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100096</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Fiskgjuse</t>
-        </is>
+        <v>102995</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -840,7 +825,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338023</v>
+        <v>337961</v>
       </c>
       <c r="R3" t="n">
-        <v>6489720</v>
+        <v>6489866</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,12 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122286958</v>
+        <v>122286962</v>
       </c>
       <c r="B4" t="n">
-        <v>57784</v>
+        <v>57713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,25 +932,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Stare</t>
-        </is>
+        <v>103008</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -970,7 +955,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -979,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337979</v>
+        <v>338073</v>
       </c>
       <c r="R4" t="n">
-        <v>6489830</v>
+        <v>6489723</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1014,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,12 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:39</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,11 +1058,6 @@
       <c r="E5" t="n">
         <v>102626</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Törnskata</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Lanius collurio</t>
@@ -1195,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122286962</v>
+        <v>122286958</v>
       </c>
       <c r="B6" t="n">
-        <v>57713</v>
+        <v>57784</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,25 +1182,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103008</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ärtsångare</t>
-        </is>
+        <v>103037</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1235,7 +1205,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338073</v>
+        <v>337979</v>
       </c>
       <c r="R6" t="n">
-        <v>6489723</v>
+        <v>6489830</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1279,7 +1249,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1289,7 +1259,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122286914</v>
+        <v>122286959</v>
       </c>
       <c r="B2" t="n">
-        <v>57221</v>
+        <v>57886</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,15 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100096</v>
+        <v>102995</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -705,7 +710,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338023</v>
+        <v>337961</v>
       </c>
       <c r="R2" t="n">
-        <v>6489720</v>
+        <v>6489866</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286959</v>
+        <v>122286958</v>
       </c>
       <c r="B3" t="n">
-        <v>57882</v>
+        <v>57788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,35 +817,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102995</v>
+        <v>103037</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337961</v>
+        <v>337979</v>
       </c>
       <c r="R3" t="n">
-        <v>6489866</v>
+        <v>6489830</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +899,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122286962</v>
+        <v>122286957</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,20 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103008</v>
+        <v>102626</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -953,9 +973,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338073</v>
+        <v>337947</v>
       </c>
       <c r="R4" t="n">
-        <v>6489723</v>
+        <v>6489822</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122286957</v>
+        <v>122286914</v>
       </c>
       <c r="B5" t="n">
-        <v>57474</v>
+        <v>57225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,16 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102626</v>
+        <v>100096</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fiskgjuse</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1073,26 +1108,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337947</v>
+        <v>338023</v>
       </c>
       <c r="R5" t="n">
-        <v>6489822</v>
+        <v>6489720</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1159,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1170,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122286958</v>
+        <v>122286962</v>
       </c>
       <c r="B6" t="n">
-        <v>57784</v>
+        <v>57717</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,20 +1207,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103037</v>
+        <v>103008</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1205,7 +1235,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1214,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337979</v>
+        <v>338073</v>
       </c>
       <c r="R6" t="n">
-        <v>6489830</v>
+        <v>6489723</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1249,7 +1279,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1259,12 +1289,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:39</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122286957</v>
+        <v>122286962</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57717</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102626</v>
+        <v>103008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,14 +973,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337947</v>
+        <v>338073</v>
       </c>
       <c r="R4" t="n">
-        <v>6489822</v>
+        <v>6489723</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1024,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:39</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122286914</v>
+        <v>122286957</v>
       </c>
       <c r="B5" t="n">
-        <v>57225</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,21 +1076,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100096</v>
+        <v>102626</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1108,16 +1098,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338023</v>
+        <v>337947</v>
       </c>
       <c r="R5" t="n">
-        <v>6489720</v>
+        <v>6489822</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122286962</v>
+        <v>122286914</v>
       </c>
       <c r="B6" t="n">
-        <v>57717</v>
+        <v>57225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,20 +1207,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103008</v>
+        <v>100096</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1233,21 +1233,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338073</v>
+        <v>338023</v>
       </c>
       <c r="R6" t="n">
-        <v>6489723</v>
+        <v>6489720</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1279,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1289,7 +1284,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122286959</v>
+        <v>122286914</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102995</v>
+        <v>100096</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,17 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337961</v>
+        <v>338023</v>
       </c>
       <c r="R2" t="n">
-        <v>6489866</v>
+        <v>6489720</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286958</v>
+        <v>122286962</v>
       </c>
       <c r="B3" t="n">
-        <v>57788</v>
+        <v>57717</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103037</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,7 +840,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337979</v>
+        <v>338073</v>
       </c>
       <c r="R3" t="n">
-        <v>6489830</v>
+        <v>6489723</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,12 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122286962</v>
+        <v>122286958</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>57788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103008</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,7 +965,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338073</v>
+        <v>337979</v>
       </c>
       <c r="R4" t="n">
-        <v>6489723</v>
+        <v>6489830</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1019,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1019,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1195,10 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122286914</v>
+        <v>122286959</v>
       </c>
       <c r="B6" t="n">
-        <v>57225</v>
+        <v>57886</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,20 +1202,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100096</v>
+        <v>102995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1230,7 +1225,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1239,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338023</v>
+        <v>337961</v>
       </c>
       <c r="R6" t="n">
-        <v>6489720</v>
+        <v>6489866</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1274,7 +1279,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,12 +1289,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286962</v>
+        <v>122286957</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>102626</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,9 +838,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338073</v>
+        <v>337947</v>
       </c>
       <c r="R3" t="n">
-        <v>6489723</v>
+        <v>6489822</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +899,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122286958</v>
+        <v>122286959</v>
       </c>
       <c r="B4" t="n">
-        <v>57788</v>
+        <v>57886</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,35 +947,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>102995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337979</v>
+        <v>337961</v>
       </c>
       <c r="R4" t="n">
-        <v>6489830</v>
+        <v>6489866</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,12 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:39</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122286957</v>
+        <v>122286958</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,20 +1077,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102626</v>
+        <v>103037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1093,11 +1103,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>obs i häcktid, lämplig biotop</t>
@@ -1109,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337947</v>
+        <v>337979</v>
       </c>
       <c r="R5" t="n">
-        <v>6489822</v>
+        <v>6489830</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122286959</v>
+        <v>122286962</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57717</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1206,16 +1211,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102995</v>
+        <v>103008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1225,12 +1230,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337961</v>
+        <v>338073</v>
       </c>
       <c r="R6" t="n">
-        <v>6489866</v>
+        <v>6489723</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122286914</v>
+        <v>122286958</v>
       </c>
       <c r="B2" t="n">
-        <v>57225</v>
+        <v>57788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100096</v>
+        <v>103037</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338023</v>
+        <v>337979</v>
       </c>
       <c r="R2" t="n">
-        <v>6489720</v>
+        <v>6489830</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286957</v>
+        <v>122286959</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57886</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,40 +817,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102626</v>
+        <v>102995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337947</v>
+        <v>337961</v>
       </c>
       <c r="R3" t="n">
-        <v>6489822</v>
+        <v>6489866</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,12 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122286959</v>
+        <v>122286957</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,40 +947,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102995</v>
+        <v>102626</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337961</v>
+        <v>337947</v>
       </c>
       <c r="R4" t="n">
-        <v>6489866</v>
+        <v>6489822</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122286958</v>
+        <v>122286914</v>
       </c>
       <c r="B5" t="n">
-        <v>57788</v>
+        <v>57225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,25 +1082,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103037</v>
+        <v>100096</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1103,21 +1108,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337979</v>
+        <v>338023</v>
       </c>
       <c r="R5" t="n">
-        <v>6489830</v>
+        <v>6489720</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122286958</v>
       </c>
       <c r="B2" t="n">
-        <v>57788</v>
+        <v>57789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286959</v>
+        <v>122286957</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57479</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,40 +817,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102995</v>
+        <v>102626</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337961</v>
+        <v>337947</v>
       </c>
       <c r="R3" t="n">
-        <v>6489866</v>
+        <v>6489822</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122286957</v>
+        <v>122286962</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57718</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +952,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102626</v>
+        <v>103008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,14 +978,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337947</v>
+        <v>338073</v>
       </c>
       <c r="R4" t="n">
-        <v>6489822</v>
+        <v>6489723</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:39</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,7 +1068,7 @@
         <v>122286914</v>
       </c>
       <c r="B5" t="n">
-        <v>57225</v>
+        <v>57226</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122286962</v>
+        <v>122286959</v>
       </c>
       <c r="B6" t="n">
-        <v>57717</v>
+        <v>57887</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,16 +1206,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103008</v>
+        <v>102995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1230,7 +1225,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338073</v>
+        <v>337961</v>
       </c>
       <c r="R6" t="n">
-        <v>6489723</v>
+        <v>6489866</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62182-2020 artfynd.xlsx
+++ b/artfynd/A 62182-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122286958</v>
+        <v>122286962</v>
       </c>
       <c r="B2" t="n">
-        <v>57789</v>
+        <v>57718</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103037</v>
+        <v>103008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337979</v>
+        <v>338073</v>
       </c>
       <c r="R2" t="n">
-        <v>6489830</v>
+        <v>6489723</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:39</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286957</v>
+        <v>122286914</v>
       </c>
       <c r="B3" t="n">
-        <v>57479</v>
+        <v>57226</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102626</v>
+        <v>100096</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,26 +838,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337947</v>
+        <v>338023</v>
       </c>
       <c r="R3" t="n">
-        <v>6489822</v>
+        <v>6489720</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -940,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122286962</v>
+        <v>122286959</v>
       </c>
       <c r="B4" t="n">
-        <v>57718</v>
+        <v>57887</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,16 +941,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103008</v>
+        <v>102995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -975,7 +960,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -989,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338073</v>
+        <v>337961</v>
       </c>
       <c r="R4" t="n">
-        <v>6489723</v>
+        <v>6489866</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1024,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122286914</v>
+        <v>122286958</v>
       </c>
       <c r="B5" t="n">
-        <v>57226</v>
+        <v>57789</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,25 +1067,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100096</v>
+        <v>103037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1103,16 +1093,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hakerud, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338023</v>
+        <v>337979</v>
       </c>
       <c r="R5" t="n">
-        <v>6489720</v>
+        <v>6489830</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1144,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1149,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1190,10 +1185,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122286959</v>
+        <v>122286957</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57479</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1202,40 +1197,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102995</v>
+        <v>102626</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337961</v>
+        <v>337947</v>
       </c>
       <c r="R6" t="n">
-        <v>6489866</v>
+        <v>6489822</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1279,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1289,7 +1284,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
